--- a/thanhvien.xlsx
+++ b/thanhvien.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/howl/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nguyenhoang/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D611F83-4C84-AA45-99FD-61F20B4B94A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41F9B2C-9B05-7848-9DD0-875AAAF4B88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1036,7 +1036,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S45"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.83203125" customWidth="1"/>
@@ -1518,276 +1518,350 @@
       <c r="K15" s="2"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="9"/>
+      <c r="A16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16">
+        <v>2006</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16">
+        <v>2024</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="I16" s="3"/>
+      <c r="J16" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K16" s="2"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="3"/>
+      <c r="A17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17">
+        <v>2004</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17">
+        <v>2025</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K17" s="2"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
+      <c r="A18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="4">
+        <v>2002</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="4">
+        <v>2020</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I18" s="3"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="3"/>
+      <c r="J18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K18" s="2"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
+      <c r="A19" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="3">
+        <v>2005</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" s="3">
+        <v>2024</v>
+      </c>
+      <c r="G19" t="s">
+        <v>54</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="I19" s="3"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="2"/>
+    </row>
+    <row r="20" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="3">
+        <v>2006</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" s="3">
+        <v>2024</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="I20" s="3"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21">
-        <v>2006</v>
+        <v>15</v>
+      </c>
+      <c r="C21" s="3">
+        <v>2005</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F21">
-        <v>2024</v>
+        <v>32</v>
+      </c>
+      <c r="F21" s="3">
+        <v>2023</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="I21" s="3"/>
-      <c r="J21" s="5" t="s">
-        <v>74</v>
-      </c>
+      <c r="J21" s="2"/>
       <c r="K21" s="2"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+      <c r="S21" s="3"/>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22">
-        <v>2004</v>
+        <v>15</v>
+      </c>
+      <c r="C22" s="3">
+        <v>2000</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F22">
-        <v>2025</v>
+        <v>32</v>
+      </c>
+      <c r="F22" s="3">
+        <v>2023</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>54</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>75</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="I22" s="3"/>
+      <c r="J22" s="2"/>
       <c r="K22" s="2"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
-        <v>51</v>
+      <c r="A23" t="s">
+        <v>63</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" s="4">
-        <v>2002</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E23" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23">
+        <v>2001</v>
+      </c>
+      <c r="D23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="4">
-        <v>2020</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="F23">
+        <v>2019</v>
+      </c>
+      <c r="G23" t="s">
         <v>54</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="I23" s="3"/>
-      <c r="J23" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K23" s="2"/>
+      <c r="J23" s="2"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="C24" s="3">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="3">
-        <v>2024</v>
-      </c>
-      <c r="G24" t="s">
+        <v>2020</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="I24" s="3"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="3">
+        <v>2001</v>
+      </c>
+      <c r="D25" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F25" s="3">
+        <v>2019</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H24" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="I24" s="3"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="2"/>
-    </row>
-    <row r="25" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C25" s="3">
-        <v>2006</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F25" s="3">
-        <v>2024</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="I25" s="3"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
+      <c r="H25" s="3" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C26" s="3">
-        <v>2005</v>
+        <v>1999</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>60</v>
+        <v>141</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="F26" s="3">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H26" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="I26" s="3"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
+      <c r="H26" s="3" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>61</v>
+        <v>142</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C27" s="3">
-        <v>2000</v>
+        <v>2005</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="F27" s="3">
         <v>2023</v>
@@ -1795,293 +1869,258 @@
       <c r="G27" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H27" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="I27" s="3"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
+      <c r="H27" s="3" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>63</v>
+      <c r="A28" s="3" t="s">
+        <v>145</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C28">
-        <v>2001</v>
+        <v>15</v>
+      </c>
+      <c r="C28" s="3">
+        <v>2005</v>
       </c>
       <c r="D28" t="s">
         <v>22</v>
       </c>
-      <c r="E28" t="s">
-        <v>32</v>
-      </c>
-      <c r="F28">
-        <v>2019</v>
-      </c>
-      <c r="G28" t="s">
+      <c r="E28" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F28" s="3">
+        <v>2023</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H28" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="I28" s="3"/>
-      <c r="J28" s="2"/>
+      <c r="H28" s="3" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="C29" s="3">
-        <v>2002</v>
+        <v>2025</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>32</v>
+        <v>148</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="F29" s="3">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="I29" s="3"/>
-      <c r="J29" s="2"/>
+        <v>54</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C30" s="3">
-        <v>2001</v>
-      </c>
-      <c r="D30" t="s">
-        <v>22</v>
+        <v>2000</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="F30" s="3">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>54</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C31" s="3">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>141</v>
+        <v>30</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>32</v>
       </c>
       <c r="F31" s="3">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>54</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>89</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C32" s="3">
-        <v>2005</v>
+        <v>2000</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>143</v>
+        <v>53</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="F32" s="3">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>54</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>101</v>
+        <v>153</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C33" s="3">
-        <v>2005</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="D33" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="F33" s="3">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>54</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="3">
-        <v>2025</v>
+        <v>15</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="E34" s="8" t="s">
         <v>86</v>
       </c>
       <c r="F34" s="3">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H34" s="3" t="s">
-        <v>149</v>
-      </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C35" s="3">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>32</v>
       </c>
       <c r="F35" s="3">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>159</v>
-      </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C36" s="3">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>32</v>
       </c>
       <c r="F36" s="3">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H36" s="3" t="s">
-        <v>155</v>
-      </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C37" s="3">
-        <v>2000</v>
+        <v>170</v>
+      </c>
+      <c r="B37" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37">
+        <v>2001</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E37" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E37" t="s">
         <v>32</v>
       </c>
       <c r="F37" s="3">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H37" s="3" t="s">
-        <v>153</v>
-      </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>32</v>
+        <v>172</v>
+      </c>
+      <c r="C38">
+        <v>2002</v>
       </c>
       <c r="F38" s="3">
         <v>2019</v>
@@ -2089,25 +2128,25 @@
       <c r="G38" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H38" s="3" t="s">
-        <v>162</v>
-      </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B39" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B39" t="s">
         <v>15</v>
       </c>
+      <c r="C39">
+        <v>1998</v>
+      </c>
       <c r="D39" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>86</v>
+        <v>141</v>
+      </c>
+      <c r="E39" t="s">
+        <v>32</v>
       </c>
       <c r="F39" s="3">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>54</v>
@@ -2115,130 +2154,24 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B40" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B40" t="s">
         <v>15</v>
       </c>
-      <c r="C40" s="3">
-        <v>1998</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E40" s="3" t="s">
+      <c r="C40">
+        <v>2001</v>
+      </c>
+      <c r="D40" t="s">
+        <v>171</v>
+      </c>
+      <c r="E40" t="s">
         <v>32</v>
       </c>
       <c r="F40" s="3">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C41" s="3">
-        <v>2001</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F41" s="3">
-        <v>2019</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B42" t="s">
-        <v>29</v>
-      </c>
-      <c r="C42">
-        <v>2001</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E42" t="s">
-        <v>32</v>
-      </c>
-      <c r="F42" s="3">
-        <v>2019</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C43">
-        <v>2002</v>
-      </c>
-      <c r="F43" s="3">
-        <v>2019</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B44" t="s">
-        <v>15</v>
-      </c>
-      <c r="C44">
-        <v>1998</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E44" t="s">
-        <v>32</v>
-      </c>
-      <c r="F44" s="3">
-        <v>2017</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B45" t="s">
-        <v>15</v>
-      </c>
-      <c r="C45">
-        <v>2001</v>
-      </c>
-      <c r="D45" t="s">
-        <v>171</v>
-      </c>
-      <c r="E45" t="s">
-        <v>32</v>
-      </c>
-      <c r="F45" s="3">
-        <v>2019</v>
-      </c>
-      <c r="G45" s="3" t="s">
         <v>54</v>
       </c>
     </row>

--- a/thanhvien.xlsx
+++ b/thanhvien.xlsx
@@ -225,7 +225,7 @@
     <t>Công nghệ sinh học</t>
   </si>
   <si>
-    <t>Quản Lí</t>
+    <t>Quản Lý</t>
   </si>
   <si>
     <t>khoi.jpg</t>
@@ -2809,6 +2809,9 @@
   <sheetPr/>
   <dimension ref="A1:N5"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.4" outlineLevelRow="4"/>
+  <cols>
+    <col min="1" max="1" width="24.7777777777778" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
